--- a/www/flightdata/xlsx/eoss-312.xlsx
+++ b/www/flightdata/xlsx/eoss-312.xlsx
@@ -3609,7 +3609,7 @@
         <v>30091.68</v>
       </c>
       <c r="I2">
-        <v>640</v>
+        <v>465</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
